--- a/tests/integration_workspace/review_classification_full/output/BUSINESS_METRICS.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/BUSINESS_METRICS.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/tests/integration_workspace/review_classification_full/output/BUSINESS_METRICS.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/BUSINESS_METRICS.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
